--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487574_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487574_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.0267</v>
+        <v>3.7003</v>
       </c>
       <c r="E2" t="n">
-        <v>3.8908</v>
+        <v>2.3128</v>
       </c>
       <c r="F2" t="n">
-        <v>2.136</v>
+        <v>1.3875</v>
       </c>
       <c r="G2" t="n">
         <v>2.3216</v>
@@ -610,13 +610,13 @@
         <v>1.1751</v>
       </c>
       <c r="S2" t="n">
-        <v>3.8226</v>
+        <v>1.4962</v>
       </c>
       <c r="T2" t="n">
-        <v>2.2714</v>
+        <v>0.6934</v>
       </c>
       <c r="U2" t="n">
-        <v>1.5513</v>
+        <v>0.8028</v>
       </c>
       <c r="V2" t="n">
         <v>0.6659</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.3359</v>
+        <v>2.5956</v>
       </c>
       <c r="E3" t="n">
-        <v>1.0213</v>
+        <v>2.1205</v>
       </c>
       <c r="F3" t="n">
-        <v>0.3147</v>
+        <v>0.4751</v>
       </c>
       <c r="G3" t="n">
         <v>-0.9052</v>
@@ -688,13 +688,13 @@
         <v>2.9377</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.9494</v>
+        <v>0.3102</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.3904</v>
+        <v>-0.2911</v>
       </c>
       <c r="U3" t="n">
-        <v>0.441</v>
+        <v>0.6014</v>
       </c>
       <c r="V3" t="n">
         <v>1.4279</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.0522</v>
+        <v>0.3096</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.4049</v>
+        <v>0.0638</v>
       </c>
       <c r="F4" t="n">
-        <v>0.3527</v>
+        <v>0.2458</v>
       </c>
       <c r="G4" t="n">
         <v>-0.4537</v>
@@ -766,13 +766,13 @@
         <v>0.7834</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.1066</v>
+        <v>0.2553</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.4158</v>
+        <v>0.0529</v>
       </c>
       <c r="U4" t="n">
-        <v>0.3092</v>
+        <v>0.2023</v>
       </c>
       <c r="V4" t="n">
         <v>-0.2754</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.16</v>
+        <v>-0.3471</v>
       </c>
       <c r="E5" t="n">
         <v>-1.0386</v>
       </c>
       <c r="F5" t="n">
-        <v>0.8786</v>
+        <v>0.6915</v>
       </c>
       <c r="G5" t="n">
         <v>0.4093</v>
@@ -844,13 +844,13 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>0.4099</v>
+        <v>0.2228</v>
       </c>
       <c r="T5" t="n">
         <v>-0.0594</v>
       </c>
       <c r="U5" t="n">
-        <v>0.4693</v>
+        <v>0.2822</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.5758</v>
+        <v>-0.4957</v>
       </c>
       <c r="E6" t="n">
         <v>-1.0386</v>
       </c>
       <c r="F6" t="n">
-        <v>0.4628</v>
+        <v>0.543</v>
       </c>
       <c r="G6" t="n">
         <v>0.4093</v>
@@ -922,13 +922,13 @@
         <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.0059</v>
+        <v>0.0743</v>
       </c>
       <c r="T6" t="n">
         <v>-0.0594</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0535</v>
+        <v>0.1337</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-2.147</v>
+        <v>-2.042</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.705</v>
+        <v>-2.2792</v>
       </c>
       <c r="F7" t="n">
-        <v>0.5580000000000001</v>
+        <v>0.2372</v>
       </c>
       <c r="G7" t="n">
         <v>-2.9665</v>
@@ -1000,13 +1000,13 @@
         <v>2.9377</v>
       </c>
       <c r="S7" t="n">
-        <v>0.4331</v>
+        <v>0.5381</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.607</v>
+        <v>-0.1812</v>
       </c>
       <c r="U7" t="n">
-        <v>1.0401</v>
+        <v>0.7193000000000001</v>
       </c>
       <c r="V7" t="n">
         <v>-0.397</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-3.3155</v>
+        <v>-3.0585</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.4282</v>
+        <v>-1.4117</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.8874</v>
+        <v>-1.6468</v>
       </c>
       <c r="G8" t="n">
         <v>-4.3221</v>
@@ -1078,13 +1078,13 @@
         <v>1.9585</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.0837</v>
+        <v>0.1734</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.1206</v>
+        <v>-0.1041</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0369</v>
+        <v>0.2775</v>
       </c>
       <c r="V8" t="n">
         <v>-0.6724</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-4.7923</v>
+        <v>-4.262</v>
       </c>
       <c r="E9" t="n">
-        <v>-5.7747</v>
+        <v>-5.6989</v>
       </c>
       <c r="F9" t="n">
-        <v>0.9825</v>
+        <v>1.4369</v>
       </c>
       <c r="G9" t="n">
         <v>-0.2853</v>
@@ -1156,13 +1156,13 @@
         <v>2.7419</v>
       </c>
       <c r="S9" t="n">
-        <v>0.0765</v>
+        <v>0.6068</v>
       </c>
       <c r="T9" t="n">
-        <v>0.3899</v>
+        <v>0.4658</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.3134</v>
+        <v>0.141</v>
       </c>
       <c r="V9" t="n">
         <v>0.7044</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.8272</v>
+        <v>-4.2852</v>
       </c>
       <c r="E10" t="n">
-        <v>-5.8104</v>
+        <v>-5.5893</v>
       </c>
       <c r="F10" t="n">
-        <v>0.9832</v>
+        <v>1.304</v>
       </c>
       <c r="G10" t="n">
         <v>-3.4825</v>
@@ -1234,13 +1234,13 @@
         <v>2.1543</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.2437</v>
+        <v>0.2982</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.1141</v>
+        <v>0.107</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.1296</v>
+        <v>0.1911</v>
       </c>
       <c r="V10" t="n">
         <v>-0.1217</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-6.8279</v>
+        <v>-6.5592</v>
       </c>
       <c r="E11" t="n">
-        <v>-5.7016</v>
+        <v>-5.5399</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.1263</v>
+        <v>-1.0193</v>
       </c>
       <c r="G11" t="n">
         <v>-2.8132</v>
@@ -1312,13 +1312,13 @@
         <v>2.9377</v>
       </c>
       <c r="S11" t="n">
-        <v>0.6524</v>
+        <v>0.921</v>
       </c>
       <c r="T11" t="n">
-        <v>0.0641</v>
+        <v>0.2258</v>
       </c>
       <c r="U11" t="n">
-        <v>0.5883</v>
+        <v>0.6952</v>
       </c>
       <c r="V11" t="n">
         <v>-2.7086</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-15.3353</v>
+        <v>-14.4442</v>
       </c>
       <c r="E12" t="n">
-        <v>-18.9899</v>
+        <v>-18.0991</v>
       </c>
       <c r="F12" t="n">
-        <v>3.6548</v>
+        <v>3.6549</v>
       </c>
       <c r="G12" t="n">
         <v>-12.0883</v>
@@ -1390,13 +1390,13 @@
         <v>17.6263</v>
       </c>
       <c r="S12" t="n">
-        <v>4.005199999999999</v>
+        <v>4.8963</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.04130000000000017</v>
+        <v>0.8497</v>
       </c>
       <c r="U12" t="n">
-        <v>4.046600000000001</v>
+        <v>4.0465</v>
       </c>
       <c r="V12" t="n">
         <v>-1.3769</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>P. FERNANDEZ GONZALEZ</t>
+          <t>I. SAMA PEREZ</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>5.1756</v>
+        <v>5.6614</v>
       </c>
       <c r="E13" t="n">
-        <v>1.8441</v>
+        <v>1.7356</v>
       </c>
       <c r="F13" t="n">
-        <v>3.3316</v>
+        <v>3.9258</v>
       </c>
       <c r="G13" t="n">
-        <v>2.6697</v>
+        <v>3.8186</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.0581</v>
+        <v>2.1423</v>
       </c>
       <c r="I13" t="n">
-        <v>2.7278</v>
+        <v>1.6763</v>
       </c>
       <c r="J13" t="n">
-        <v>2.851</v>
+        <v>2.8469</v>
       </c>
       <c r="K13" t="n">
-        <v>0.4116</v>
+        <v>1.7267</v>
       </c>
       <c r="L13" t="n">
-        <v>2.4394</v>
+        <v>1.1201</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.1813</v>
+        <v>0.9718</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.4698</v>
+        <v>0.4156</v>
       </c>
       <c r="O13" t="n">
-        <v>0.2885</v>
+        <v>0.5562</v>
       </c>
       <c r="P13" t="n">
-        <v>-0.7834</v>
+        <v>1.3709</v>
       </c>
       <c r="Q13" t="n">
-        <v>-3.917</v>
+        <v>-1.9585</v>
       </c>
       <c r="R13" t="n">
-        <v>3.1336</v>
+        <v>3.3294</v>
       </c>
       <c r="S13" t="n">
-        <v>0.0301</v>
+        <v>-0.1364</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.6246</v>
+        <v>-0.3694</v>
       </c>
       <c r="U13" t="n">
-        <v>0.6546999999999999</v>
+        <v>0.2329</v>
       </c>
       <c r="V13" t="n">
-        <v>3.2593</v>
+        <v>0.6083</v>
       </c>
       <c r="W13" t="n">
-        <v>3.5346</v>
+        <v>1.2166</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.2754</v>
+        <v>-0.6083</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>I. SAMA PEREZ</t>
+          <t>P. FERNANDEZ GONZALEZ</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>5.0973</v>
+        <v>4.8226</v>
       </c>
       <c r="E14" t="n">
-        <v>1.7356</v>
+        <v>1.4347</v>
       </c>
       <c r="F14" t="n">
-        <v>3.3617</v>
+        <v>3.3878</v>
       </c>
       <c r="G14" t="n">
-        <v>3.8186</v>
+        <v>2.6697</v>
       </c>
       <c r="H14" t="n">
-        <v>2.1423</v>
+        <v>-0.0581</v>
       </c>
       <c r="I14" t="n">
-        <v>1.6763</v>
+        <v>2.7278</v>
       </c>
       <c r="J14" t="n">
-        <v>2.8469</v>
+        <v>2.851</v>
       </c>
       <c r="K14" t="n">
-        <v>1.7267</v>
+        <v>0.4116</v>
       </c>
       <c r="L14" t="n">
-        <v>1.1201</v>
+        <v>2.4394</v>
       </c>
       <c r="M14" t="n">
-        <v>0.9718</v>
+        <v>-0.1813</v>
       </c>
       <c r="N14" t="n">
-        <v>0.4156</v>
+        <v>-0.4698</v>
       </c>
       <c r="O14" t="n">
-        <v>0.5562</v>
+        <v>0.2885</v>
       </c>
       <c r="P14" t="n">
-        <v>1.3709</v>
+        <v>-0.7834</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.9585</v>
+        <v>-3.917</v>
       </c>
       <c r="R14" t="n">
-        <v>3.3294</v>
+        <v>3.1336</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.7006</v>
+        <v>-0.323</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.3694</v>
+        <v>-1.0339</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.3312</v>
+        <v>0.7109</v>
       </c>
       <c r="V14" t="n">
-        <v>0.6083</v>
+        <v>3.2593</v>
       </c>
       <c r="W14" t="n">
-        <v>1.2166</v>
+        <v>3.5346</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.6083</v>
+        <v>-0.2754</v>
       </c>
     </row>
     <row r="15">
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.0859</v>
+        <v>3.7909</v>
       </c>
       <c r="E15" t="n">
-        <v>2.1975</v>
+        <v>1.6858</v>
       </c>
       <c r="F15" t="n">
-        <v>1.8885</v>
+        <v>2.1051</v>
       </c>
       <c r="G15" t="n">
         <v>1.6552</v>
@@ -1624,13 +1624,13 @@
         <v>2.546</v>
       </c>
       <c r="S15" t="n">
-        <v>0.3969</v>
+        <v>0.1019</v>
       </c>
       <c r="T15" t="n">
-        <v>0.6693</v>
+        <v>0.1576</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.2724</v>
+        <v>-0.0557</v>
       </c>
       <c r="V15" t="n">
         <v>-0.5122</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.6635</v>
+        <v>3.6396</v>
       </c>
       <c r="E16" t="n">
         <v>0.2103</v>
       </c>
       <c r="F16" t="n">
-        <v>3.4532</v>
+        <v>3.4293</v>
       </c>
       <c r="G16" t="n">
         <v>4.7859</v>
@@ -1702,13 +1702,13 @@
         <v>2.1543</v>
       </c>
       <c r="S16" t="n">
-        <v>0.4871</v>
+        <v>0.4632</v>
       </c>
       <c r="T16" t="n">
         <v>-0.1911</v>
       </c>
       <c r="U16" t="n">
-        <v>0.6782</v>
+        <v>0.6543</v>
       </c>
       <c r="V16" t="n">
         <v>-0.8260999999999999</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. SYTAR</t>
+          <t>J. ARGENTI</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.9253</v>
+        <v>2.4431</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.8300999999999999</v>
+        <v>1.1072</v>
       </c>
       <c r="F17" t="n">
-        <v>2.7555</v>
+        <v>1.3359</v>
       </c>
       <c r="G17" t="n">
-        <v>0.7289</v>
+        <v>2.206</v>
       </c>
       <c r="H17" t="n">
-        <v>0.9562</v>
+        <v>-0.345</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.2273</v>
+        <v>2.551</v>
       </c>
       <c r="J17" t="n">
-        <v>0.7737000000000001</v>
+        <v>1.93</v>
       </c>
       <c r="K17" t="n">
-        <v>1.2895</v>
+        <v>0.0612</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.5158</v>
+        <v>1.8687</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.0449</v>
+        <v>0.276</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.3333</v>
+        <v>-0.4062</v>
       </c>
       <c r="O17" t="n">
-        <v>0.2885</v>
+        <v>0.6822</v>
       </c>
       <c r="P17" t="n">
-        <v>1.7626</v>
+        <v>0.5875</v>
       </c>
       <c r="Q17" t="n">
         <v>-0.9792</v>
       </c>
       <c r="R17" t="n">
-        <v>2.7419</v>
+        <v>1.5668</v>
       </c>
       <c r="S17" t="n">
-        <v>0.0421</v>
+        <v>-0.2288</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.6246</v>
+        <v>0.1564</v>
       </c>
       <c r="U17" t="n">
-        <v>0.6667</v>
+        <v>-0.3852</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.6083</v>
+        <v>-0.1217</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.6083</v>
+        <v>-0.1217</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>J. ARGENTI</t>
+          <t>A. SYTAR</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.6926</v>
+        <v>1.5409</v>
       </c>
       <c r="E18" t="n">
-        <v>0.4932</v>
+        <v>-1.1371</v>
       </c>
       <c r="F18" t="n">
-        <v>1.1995</v>
+        <v>2.6781</v>
       </c>
       <c r="G18" t="n">
-        <v>2.206</v>
+        <v>0.7289</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.345</v>
+        <v>0.9562</v>
       </c>
       <c r="I18" t="n">
-        <v>2.551</v>
+        <v>-0.2273</v>
       </c>
       <c r="J18" t="n">
-        <v>1.93</v>
+        <v>0.7737000000000001</v>
       </c>
       <c r="K18" t="n">
-        <v>0.0612</v>
+        <v>1.2895</v>
       </c>
       <c r="L18" t="n">
-        <v>1.8687</v>
+        <v>-0.5158</v>
       </c>
       <c r="M18" t="n">
-        <v>0.276</v>
+        <v>-0.0449</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.4062</v>
+        <v>-0.3333</v>
       </c>
       <c r="O18" t="n">
-        <v>0.6822</v>
+        <v>0.2885</v>
       </c>
       <c r="P18" t="n">
-        <v>0.5875</v>
+        <v>1.7626</v>
       </c>
       <c r="Q18" t="n">
         <v>-0.9792</v>
       </c>
       <c r="R18" t="n">
-        <v>1.5668</v>
+        <v>2.7419</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.9792</v>
+        <v>-0.3423</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.4576</v>
+        <v>-0.9316</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.5217000000000001</v>
+        <v>0.5893</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.1217</v>
+        <v>-0.6083</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.1217</v>
+        <v>-0.6083</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>M. FERNANDEZ LOPEZ</t>
+          <t>C. DARRIBA VAZQUEZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.3145</v>
+        <v>0.5717</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.8604000000000001</v>
+        <v>-1.0189</v>
       </c>
       <c r="F19" t="n">
-        <v>0.546</v>
+        <v>1.5906</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.5458</v>
+        <v>2.4928</v>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>0.6081</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.5458</v>
+        <v>1.8847</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.6822</v>
+        <v>2.7407</v>
       </c>
       <c r="K19" t="n">
-        <v>0</v>
+        <v>1.281</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.6822</v>
+        <v>1.4598</v>
       </c>
       <c r="M19" t="n">
-        <v>0.1364</v>
+        <v>-0.248</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>-0.6729000000000001</v>
       </c>
       <c r="O19" t="n">
-        <v>0.1364</v>
+        <v>0.4249</v>
       </c>
       <c r="P19" t="n">
-        <v>0.3917</v>
+        <v>-0.3917</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-3.917</v>
       </c>
       <c r="R19" t="n">
-        <v>0.3917</v>
+        <v>3.5253</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.1604</v>
+        <v>-0.7994</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.1782</v>
+        <v>-1.0592</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0178</v>
+        <v>0.2598</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>-0.73</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.2166</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-1.9466</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>C. DARRIBA VAZQUEZ</t>
+          <t>M. FERNANDEZ LOPEZ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.3557</v>
+        <v>-0.2877</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.3259</v>
+        <v>-0.8604000000000001</v>
       </c>
       <c r="F20" t="n">
-        <v>0.9702</v>
+        <v>0.5727</v>
       </c>
       <c r="G20" t="n">
-        <v>2.4928</v>
+        <v>-0.5458</v>
       </c>
       <c r="H20" t="n">
-        <v>0.6081</v>
+        <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>1.8847</v>
+        <v>-0.5458</v>
       </c>
       <c r="J20" t="n">
-        <v>2.7407</v>
+        <v>-0.6822</v>
       </c>
       <c r="K20" t="n">
-        <v>1.281</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>1.4598</v>
+        <v>-0.6822</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.248</v>
+        <v>0.1364</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.6729000000000001</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>0.4249</v>
+        <v>0.1364</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.3917</v>
+        <v>0.3917</v>
       </c>
       <c r="Q20" t="n">
-        <v>-3.917</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>3.5253</v>
+        <v>0.3917</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.7268</v>
+        <v>-0.1337</v>
       </c>
       <c r="T20" t="n">
-        <v>-1.3662</v>
+        <v>-0.1782</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.3606</v>
+        <v>0.0446</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.73</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>1.2166</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.9466</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.6238</v>
+        <v>-2.5233</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.8237</v>
+        <v>-2.619</v>
       </c>
       <c r="F21" t="n">
-        <v>0.1999</v>
+        <v>0.0958</v>
       </c>
       <c r="G21" t="n">
         <v>-4.4253</v>
@@ -2092,13 +2092,13 @@
         <v>1.7626</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.0561</v>
+        <v>-0.9556</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.8316</v>
+        <v>-0.627</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.2245</v>
+        <v>-0.3286</v>
       </c>
       <c r="V21" t="n">
         <v>1.0949</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.0111</v>
+        <v>-2.9594</v>
       </c>
       <c r="E22" t="n">
-        <v>-4.2953</v>
+        <v>-4.1929</v>
       </c>
       <c r="F22" t="n">
-        <v>1.2842</v>
+        <v>1.2335</v>
       </c>
       <c r="G22" t="n">
         <v>-1.2978</v>
@@ -2170,13 +2170,13 @@
         <v>2.3502</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.3382</v>
+        <v>-0.2866</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.0723</v>
+        <v>0.03</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.2659</v>
+        <v>-0.3166</v>
       </c>
       <c r="V22" t="n">
         <v>-0.7875</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>15.3351</v>
+        <v>16.69980000000001</v>
       </c>
       <c r="E23" t="n">
         <v>-3.654700000000001</v>
       </c>
       <c r="F23" t="n">
-        <v>18.9903</v>
+        <v>20.3546</v>
       </c>
       <c r="G23" t="n">
         <v>12.0882</v>
@@ -2248,13 +2248,13 @@
         <v>23.5018</v>
       </c>
       <c r="S23" t="n">
-        <v>-4.0051</v>
+        <v>-2.6407</v>
       </c>
       <c r="T23" t="n">
-        <v>-4.0463</v>
+        <v>-4.046399999999999</v>
       </c>
       <c r="U23" t="n">
-        <v>0.04109999999999991</v>
+        <v>1.4057</v>
       </c>
       <c r="V23" t="n">
         <v>1.3767</v>
